--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.1079,0.5861,0.5515,0.0226</t>
-  </si>
-  <si>
-    <t>0.1274,0.4200,0.6728,0.0436</t>
-  </si>
-  <si>
-    <t>0.0693,0.5781,0.6636,0.0152</t>
-  </si>
-  <si>
-    <t>0.0945,0.6543,0.5725,0.0271</t>
-  </si>
-  <si>
-    <t>0.0779,0.5738,0.6673,0.0147</t>
-  </si>
-  <si>
-    <t>0.0819,0.5245,0.6498,0.0095</t>
-  </si>
-  <si>
-    <t>0.0725,0.6844,0.5794,0.0165</t>
-  </si>
-  <si>
-    <t>0.1260,0.6499,0.4468,0.0214</t>
-  </si>
-  <si>
-    <t>0.0946,0.6352,0.6105,0.0210</t>
-  </si>
-  <si>
-    <t>0.1033,0.5187,0.5969,0.0181</t>
-  </si>
-  <si>
-    <t>0.0741,0.6262,0.6178,0.0126</t>
-  </si>
-  <si>
-    <t>0.0671,0.7054,0.5339,0.0088</t>
-  </si>
-  <si>
-    <t>0.0690,0.5378,0.7085,0.0166</t>
-  </si>
-  <si>
-    <t>0.0780,0.5161,0.7255,0.0237</t>
-  </si>
-  <si>
-    <t>0.0485,0.5226,0.7603,0.0080</t>
-  </si>
-  <si>
-    <t>0.0651,0.4192,0.7608,0.0110</t>
-  </si>
-  <si>
-    <t>0.0996,0.4377,0.7152,0.0267</t>
-  </si>
-  <si>
-    <t>0.0277,0.9222,0.3603,0.0084</t>
-  </si>
-  <si>
-    <t>0.0356,0.8706,0.3972,0.0058</t>
-  </si>
-  <si>
-    <t>0.0280,0.8726,0.4301,0.0058</t>
-  </si>
-  <si>
-    <t>0.0226,0.8280,0.6048,0.0056</t>
-  </si>
-  <si>
-    <t>0.0228,0.8839,0.5433,0.0054</t>
-  </si>
-  <si>
-    <t>0.0998,0.4419,0.7043,0.0194</t>
-  </si>
-  <si>
-    <t>0.0531,0.3813,0.8300,0.0110</t>
-  </si>
-  <si>
-    <t>0.0239,0.3510,0.8921,0.0043</t>
-  </si>
-  <si>
-    <t>0.0611,0.4521,0.7488,0.0155</t>
-  </si>
-  <si>
-    <t>0.0259,0.3660,0.8785,0.0032</t>
-  </si>
-  <si>
-    <t>0.1124,0.3288,0.7524,0.0301</t>
-  </si>
-  <si>
-    <t>0.0534,0.2911,0.8535,0.0111</t>
-  </si>
-  <si>
-    <t>0.0342,0.7774,0.6088,0.0077</t>
-  </si>
-  <si>
-    <t>0.0796,0.5636,0.6989,0.0263</t>
-  </si>
-  <si>
-    <t>0.0221,0.5141,0.8686,0.0030</t>
-  </si>
-  <si>
-    <t>0.0543,0.7668,0.5576,0.0135</t>
-  </si>
-  <si>
-    <t>0.0810,0.5427,0.6798,0.0203</t>
-  </si>
-  <si>
-    <t>0.0801,0.5926,0.5874,0.0154</t>
-  </si>
-  <si>
-    <t>0.0732,0.7429,0.5174,0.0171</t>
-  </si>
-  <si>
-    <t>0.0240,0.8830,0.5306,0.0057</t>
-  </si>
-  <si>
-    <t>0.0238,0.7087,0.8074,0.0090</t>
-  </si>
-  <si>
-    <t>0.0272,0.5963,0.8413,0.0060</t>
-  </si>
-  <si>
-    <t>0.0373,0.4697,0.8412,0.0059</t>
-  </si>
-  <si>
-    <t>0.0505,0.5513,0.7755,0.0140</t>
-  </si>
-  <si>
-    <t>0.0230,0.7627,0.7419,0.0046</t>
-  </si>
-  <si>
-    <t>0.0078,0.9712,0.3764,0.0020</t>
-  </si>
-  <si>
-    <t>0.0317,0.4622,0.8714,0.0064</t>
-  </si>
-  <si>
-    <t>0.0619,0.5845,0.6872,0.0153</t>
-  </si>
-  <si>
-    <t>0.0383,0.8295,0.5333,0.0104</t>
-  </si>
-  <si>
-    <t>0.0785,0.6524,0.5923,0.0234</t>
-  </si>
-  <si>
-    <t>0.0253,0.8272,0.6266,0.0052</t>
-  </si>
-  <si>
-    <t>0.0126,0.5014,0.9205,0.0022</t>
-  </si>
-  <si>
-    <t>0.0055,0.7360,0.9167,0.0008</t>
-  </si>
-  <si>
-    <t>0.0477,0.4173,0.8104,0.0113</t>
-  </si>
-  <si>
-    <t>0.0333,0.3036,0.8864,0.0042</t>
-  </si>
-  <si>
-    <t>0.0018,0.8638,0.9400,0.0004</t>
-  </si>
-  <si>
-    <t>0.0139,0.7088,0.8192,0.0017</t>
-  </si>
-  <si>
-    <t>0.0815,0.7179,0.4784,0.0144</t>
-  </si>
-  <si>
-    <t>0.0540,0.6977,0.6313,0.0118</t>
-  </si>
-  <si>
-    <t>0.0669,0.5339,0.6736,0.0118</t>
-  </si>
-  <si>
-    <t>0.0137,0.6665,0.8825,0.0035</t>
-  </si>
-  <si>
-    <t>0.0641,0.7341,0.5862,0.0181</t>
-  </si>
-  <si>
-    <t>0.0393,0.7924,0.5711,0.0084</t>
-  </si>
-  <si>
-    <t>0.0446,0.7446,0.6082,0.0108</t>
-  </si>
-  <si>
-    <t>0.0036,0.9514,0.7321,0.0006</t>
-  </si>
-  <si>
-    <t>0.0074,0.6700,0.9055,0.0014</t>
-  </si>
-  <si>
-    <t>0.0150,0.6344,0.8746,0.0020</t>
-  </si>
-  <si>
-    <t>0.0036,0.8735,0.8903,0.0006</t>
-  </si>
-  <si>
-    <t>0.0125,0.4973,0.9211,0.0021</t>
-  </si>
-  <si>
-    <t>0.0214,0.8989,0.5108,0.0062</t>
-  </si>
-  <si>
-    <t>0.0062,0.9787,0.2355,0.0013</t>
-  </si>
-  <si>
-    <t>0.0887,0.5568,0.6398,0.0170</t>
-  </si>
-  <si>
-    <t>0.1348,0.5762,0.5616,0.0372</t>
-  </si>
-  <si>
-    <t>0.0088,0.8056,0.7839,0.0013</t>
-  </si>
-  <si>
-    <t>0.0173,0.7111,0.8309,0.0028</t>
-  </si>
-  <si>
-    <t>0.0070,0.7975,0.8635,0.0013</t>
-  </si>
-  <si>
-    <t>0.0112,0.9410,0.5335,0.0025</t>
-  </si>
-  <si>
-    <t>0.0142,0.9211,0.5537,0.0022</t>
-  </si>
-  <si>
-    <t>0.0865,0.4128,0.7320,0.0283</t>
-  </si>
-  <si>
-    <t>0.0715,0.5195,0.7100,0.0175</t>
-  </si>
-  <si>
-    <t>0.2417,0.2503,0.6243,0.0574</t>
-  </si>
-  <si>
-    <t>0.1772,0.3178,0.6345,0.0594</t>
-  </si>
-  <si>
-    <t>0.1344,0.3276,0.6934,0.0423</t>
-  </si>
-  <si>
-    <t>0.1575,0.3583,0.6664,0.0527</t>
-  </si>
-  <si>
-    <t>0.0077,0.8094,0.8338,0.0014</t>
-  </si>
-  <si>
-    <t>0.0085,0.8756,0.7897,0.0015</t>
-  </si>
-  <si>
-    <t>0.0157,0.7876,0.7763,0.0034</t>
-  </si>
-  <si>
-    <t>0.0122,0.8205,0.8157,0.0030</t>
-  </si>
-  <si>
-    <t>0.0023,0.9122,0.8861,0.0005</t>
-  </si>
-  <si>
-    <t>0.0124,0.9059,0.5972,0.0022</t>
-  </si>
-  <si>
-    <t>0.1056,0.5452,0.6193,0.0113</t>
-  </si>
-  <si>
-    <t>0.0992,0.6690,0.4807,0.0165</t>
-  </si>
-  <si>
-    <t>0.1024,0.6417,0.5520,0.0231</t>
-  </si>
-  <si>
-    <t>0.0621,0.7385,0.5512,0.0173</t>
-  </si>
-  <si>
-    <t>0.0882,0.6209,0.6255,0.0185</t>
-  </si>
-  <si>
-    <t>0.0841,0.5970,0.6178,0.0162</t>
-  </si>
-  <si>
-    <t>0.0637,0.7280,0.5683,0.0152</t>
-  </si>
-  <si>
-    <t>0.0932,0.5584,0.6512,0.0129</t>
-  </si>
-  <si>
-    <t>0.0925,0.6395,0.5531,0.0171</t>
-  </si>
-  <si>
-    <t>0.0852,0.5751,0.6444,0.0168</t>
-  </si>
-  <si>
-    <t>0.0785,0.7492,0.4857,0.0132</t>
-  </si>
-  <si>
-    <t>0.0986,0.6727,0.4968,0.0174</t>
-  </si>
-  <si>
-    <t>0.0476,0.8047,0.5454,0.0117</t>
-  </si>
-  <si>
-    <t>0.0473,0.7242,0.6525,0.0107</t>
-  </si>
-  <si>
-    <t>0.1196,0.6006,0.5501,0.0248</t>
-  </si>
-  <si>
-    <t>0.0529,0.7022,0.6293,0.0118</t>
-  </si>
-  <si>
-    <t>0.0115,0.2848,0.9587,0.0022</t>
-  </si>
-  <si>
-    <t>0.0300,0.6335,0.7870,0.0056</t>
-  </si>
-  <si>
-    <t>0.0832,0.4382,0.7115,0.0155</t>
-  </si>
-  <si>
-    <t>0.0445,0.4835,0.8012,0.0082</t>
-  </si>
-  <si>
-    <t>0.0562,0.7601,0.5352,0.0109</t>
-  </si>
-  <si>
-    <t>0.0533,0.8250,0.4382,0.0148</t>
-  </si>
-  <si>
-    <t>0.0534,0.6830,0.6479,0.0129</t>
-  </si>
-  <si>
-    <t>0.0268,0.8171,0.6041,0.0065</t>
-  </si>
-  <si>
-    <t>0.0225,0.8957,0.4841,0.0047</t>
-  </si>
-  <si>
-    <t>0.0266,0.8624,0.4708,0.0052</t>
-  </si>
-  <si>
-    <t>0.0564,0.7729,0.5444,0.0155</t>
-  </si>
-  <si>
-    <t>0.0918,0.4178,0.7295,0.0286</t>
-  </si>
-  <si>
-    <t>0.0373,0.5294,0.7867,0.0069</t>
-  </si>
-  <si>
-    <t>0.0517,0.5230,0.7268,0.0088</t>
-  </si>
-  <si>
-    <t>0.0980,0.5010,0.6413,0.0240</t>
-  </si>
-  <si>
-    <t>0.0766,0.4314,0.7403,0.0225</t>
-  </si>
-  <si>
-    <t>0.0154,0.9321,0.5219,0.0038</t>
-  </si>
-  <si>
-    <t>0.0179,0.9263,0.5231,0.0069</t>
-  </si>
-  <si>
-    <t>0.0666,0.6482,0.6568,0.0211</t>
-  </si>
-  <si>
-    <t>0.0068,0.9644,0.4488,0.0021</t>
-  </si>
-  <si>
-    <t>0.0414,0.7801,0.5827,0.0084</t>
-  </si>
-  <si>
-    <t>0.0535,0.6281,0.6841,0.0111</t>
-  </si>
-  <si>
-    <t>0.0569,0.7974,0.4332,0.0089</t>
-  </si>
-  <si>
-    <t>0.0374,0.6048,0.7557,0.0068</t>
-  </si>
-  <si>
-    <t>0.0690,0.6488,0.6213,0.0157</t>
-  </si>
-  <si>
-    <t>0.0591,0.7213,0.6066,0.0229</t>
-  </si>
-  <si>
-    <t>0.0603,0.7287,0.5978,0.0172</t>
-  </si>
-  <si>
-    <t>0.1025,0.6233,0.5764,0.0204</t>
-  </si>
-  <si>
-    <t>0.0778,0.6111,0.6112,0.0132</t>
-  </si>
-  <si>
-    <t>0.0791,0.6210,0.6204,0.0184</t>
-  </si>
-  <si>
-    <t>0.0511,0.6755,0.6284,0.0151</t>
-  </si>
-  <si>
-    <t>0.0079,0.7775,0.8601,0.0014</t>
-  </si>
-  <si>
-    <t>0.0094,0.8570,0.8182,0.0019</t>
-  </si>
-  <si>
-    <t>0.0057,0.5587,0.9496,0.0010</t>
-  </si>
-  <si>
-    <t>0.0260,0.6288,0.7987,0.0057</t>
-  </si>
-  <si>
-    <t>0.0446,0.6332,0.6804,0.0087</t>
-  </si>
-  <si>
-    <t>0.0893,0.4535,0.6926,0.0144</t>
-  </si>
-  <si>
-    <t>0.1116,0.4228,0.6801,0.0181</t>
-  </si>
-  <si>
-    <t>0.1123,0.4997,0.6390,0.0319</t>
-  </si>
-  <si>
-    <t>0.1528,0.3954,0.6389,0.0433</t>
-  </si>
-  <si>
-    <t>0.1229,0.4369,0.6402,0.0691</t>
-  </si>
-  <si>
-    <t>0.1045,0.2941,0.7810,0.0172</t>
-  </si>
-  <si>
-    <t>0.0857,0.5615,0.6669,0.0312</t>
-  </si>
-  <si>
-    <t>0.0079,0.8925,0.7793,0.0023</t>
-  </si>
-  <si>
-    <t>0.0356,0.8030,0.6002,0.0089</t>
-  </si>
-  <si>
-    <t>0.0454,0.8113,0.4444,0.0076</t>
-  </si>
-  <si>
-    <t>0.0769,0.5746,0.6062,0.0118</t>
-  </si>
-  <si>
-    <t>0.0390,0.8243,0.5384,0.0129</t>
-  </si>
-  <si>
-    <t>0.0468,0.6896,0.6747,0.0104</t>
-  </si>
-  <si>
-    <t>0.1415,0.3908,0.6471,0.0246</t>
-  </si>
-  <si>
-    <t>0.0886,0.6409,0.5596,0.0213</t>
-  </si>
-  <si>
-    <t>0.0164,0.7605,0.8083,0.0048</t>
-  </si>
-  <si>
-    <t>0.1119,0.4288,0.6663,0.0236</t>
-  </si>
-  <si>
-    <t>0.0707,0.5893,0.6875,0.0197</t>
-  </si>
-  <si>
-    <t>0.0943,0.6146,0.6252,0.0251</t>
-  </si>
-  <si>
-    <t>0.1291,0.4840,0.5918,0.0236</t>
-  </si>
-  <si>
-    <t>0.0558,0.7671,0.4998,0.0119</t>
-  </si>
-  <si>
-    <t>0.0790,0.6361,0.6752,0.0227</t>
-  </si>
-  <si>
-    <t>0.0647,0.6029,0.6690,0.0143</t>
-  </si>
-  <si>
-    <t>0.0739,0.6313,0.6021,0.0150</t>
-  </si>
-  <si>
-    <t>0.0644,0.8050,0.4939,0.0238</t>
-  </si>
-  <si>
-    <t>0.0381,0.8019,0.5213,0.0092</t>
-  </si>
-  <si>
-    <t>0.0890,0.6810,0.5322,0.0182</t>
-  </si>
-  <si>
-    <t>0.0399,0.7303,0.6016,0.0072</t>
-  </si>
-  <si>
-    <t>0.0395,0.7328,0.6234,0.0072</t>
-  </si>
-  <si>
-    <t>0.0333,0.8232,0.6039,0.0111</t>
-  </si>
-  <si>
-    <t>0.0825,0.6712,0.5779,0.0196</t>
-  </si>
-  <si>
-    <t>0.1433,0.5623,0.5237,0.0235</t>
-  </si>
-  <si>
-    <t>0.0274,0.7941,0.6244,0.0053</t>
-  </si>
-  <si>
-    <t>0.0613,0.7904,0.4302,0.0108</t>
-  </si>
-  <si>
-    <t>0.0522,0.7878,0.5319,0.0126</t>
-  </si>
-  <si>
-    <t>0.0628,0.7311,0.5731,0.0165</t>
-  </si>
-  <si>
-    <t>0.0315,0.8188,0.5293,0.0058</t>
-  </si>
-  <si>
-    <t>0.1065,0.4948,0.6369,0.0186</t>
-  </si>
-  <si>
-    <t>0.0454,0.8208,0.4568,0.0072</t>
-  </si>
-  <si>
-    <t>0.1115,0.5315,0.6522,0.0290</t>
-  </si>
-  <si>
-    <t>0.0116,0.7458,0.8407,0.0021</t>
-  </si>
-  <si>
-    <t>0.0431,0.7086,0.6158,0.0061</t>
-  </si>
-  <si>
-    <t>0.0125,0.6864,0.8762,0.0021</t>
-  </si>
-  <si>
-    <t>0.0189,0.7243,0.7852,0.0031</t>
-  </si>
-  <si>
-    <t>0.0494,0.4883,0.7758,0.0086</t>
-  </si>
-  <si>
-    <t>0.0179,0.5388,0.8813,0.0039</t>
-  </si>
-  <si>
-    <t>0.0228,0.3472,0.9109,0.0032</t>
-  </si>
-  <si>
-    <t>0.0517,0.4701,0.7741,0.0072</t>
-  </si>
-  <si>
-    <t>0.0100,0.6140,0.8914,0.0016</t>
-  </si>
-  <si>
-    <t>0.0538,0.4267,0.7780,0.0116</t>
-  </si>
-  <si>
-    <t>0.0790,0.4174,0.7601,0.0198</t>
-  </si>
-  <si>
-    <t>0.0630,0.7430,0.5519,0.0170</t>
-  </si>
-  <si>
-    <t>0.0518,0.6242,0.7328,0.0123</t>
-  </si>
-  <si>
-    <t>0.0765,0.5635,0.6799,0.0150</t>
-  </si>
-  <si>
-    <t>0.0493,0.6633,0.7120,0.0110</t>
-  </si>
-  <si>
-    <t>0.0738,0.5635,0.6745,0.0213</t>
-  </si>
-  <si>
-    <t>0.0715,0.4643,0.7526,0.0120</t>
-  </si>
-  <si>
-    <t>0.0409,0.7599,0.5983,0.0096</t>
-  </si>
-  <si>
-    <t>0.0604,0.6944,0.5928,0.0119</t>
-  </si>
-  <si>
-    <t>0.0850,0.6438,0.5854,0.0147</t>
-  </si>
-  <si>
-    <t>0.0636,0.7443,0.5482,0.0145</t>
-  </si>
-  <si>
-    <t>0.0587,0.7168,0.6057,0.0133</t>
-  </si>
-  <si>
-    <t>0.0684,0.5390,0.7151,0.0166</t>
-  </si>
-  <si>
-    <t>0.0704,0.4591,0.7489,0.0126</t>
-  </si>
-  <si>
-    <t>0.0850,0.5633,0.6162,0.0212</t>
-  </si>
-  <si>
-    <t>0.0408,0.5510,0.7798,0.0083</t>
-  </si>
-  <si>
-    <t>0.0523,0.6430,0.6808,0.0118</t>
-  </si>
-  <si>
-    <t>0.0216,0.5350,0.8784,0.0053</t>
-  </si>
-  <si>
-    <t>0.0323,0.5429,0.8283,0.0058</t>
-  </si>
-  <si>
-    <t>0.0252,0.4030,0.9018,0.0058</t>
-  </si>
-  <si>
-    <t>0.0215,0.6135,0.8628,0.0045</t>
-  </si>
-  <si>
-    <t>0.0273,0.4955,0.8581,0.0042</t>
-  </si>
-  <si>
-    <t>0.0534,0.7162,0.6030,0.0115</t>
-  </si>
-  <si>
-    <t>0.0401,0.7333,0.6400,0.0082</t>
-  </si>
-  <si>
-    <t>0.0861,0.5709,0.6597,0.0169</t>
-  </si>
-  <si>
-    <t>0.0728,0.7497,0.5144,0.0135</t>
-  </si>
-  <si>
-    <t>0.0404,0.7585,0.6013,0.0091</t>
-  </si>
-  <si>
-    <t>0.1023,0.6298,0.5325,0.0203</t>
-  </si>
-  <si>
-    <t>0.0535,0.8189,0.4231,0.0102</t>
-  </si>
-  <si>
-    <t>0.0483,0.6816,0.6849,0.0105</t>
-  </si>
-  <si>
-    <t>0.0428,0.6845,0.6793,0.0085</t>
-  </si>
-  <si>
-    <t>0.0935,0.5155,0.6630,0.0257</t>
-  </si>
-  <si>
-    <t>0.0284,0.7557,0.6354,0.0067</t>
-  </si>
-  <si>
-    <t>0.0268,0.4504,0.8720,0.0043</t>
-  </si>
-  <si>
-    <t>0.0121,0.3596,0.9430,0.0024</t>
-  </si>
-  <si>
-    <t>0.0363,0.5588,0.7546,0.0054</t>
-  </si>
-  <si>
-    <t>0.0016,0.6623,0.9747,0.0003</t>
-  </si>
-  <si>
-    <t>0.0605,0.4894,0.7439,0.0127</t>
-  </si>
-  <si>
-    <t>0.0081,0.3461,0.9637,0.0022</t>
-  </si>
-  <si>
-    <t>0.0101,0.6192,0.9117,0.0013</t>
-  </si>
-  <si>
-    <t>0.0491,0.5099,0.7685,0.0125</t>
-  </si>
-  <si>
-    <t>0.0907,0.3781,0.7583,0.0180</t>
-  </si>
-  <si>
-    <t>0.0632,0.5017,0.7237,0.0109</t>
-  </si>
-  <si>
-    <t>0.1166,0.4231,0.6640,0.0217</t>
-  </si>
-  <si>
-    <t>0.0565,0.7617,0.5559,0.0151</t>
-  </si>
-  <si>
-    <t>0.0404,0.8018,0.5667,0.0075</t>
-  </si>
-  <si>
-    <t>0.0594,0.7227,0.5586,0.0140</t>
-  </si>
-  <si>
-    <t>0.0398,0.8102,0.5121,0.0061</t>
-  </si>
-  <si>
-    <t>0.0745,0.5907,0.6462,0.0143</t>
-  </si>
-  <si>
-    <t>0.0628,0.7654,0.5368,0.0168</t>
-  </si>
-  <si>
-    <t>0.0468,0.8368,0.4129,0.0126</t>
-  </si>
-  <si>
-    <t>0.0348,0.7921,0.5709,0.0073</t>
-  </si>
-  <si>
-    <t>0.0221,0.7806,0.6825,0.0051</t>
-  </si>
-  <si>
-    <t>0.0158,0.6335,0.8441,0.0038</t>
-  </si>
-  <si>
-    <t>0.0112,0.6288,0.9021,0.0013</t>
-  </si>
-  <si>
-    <t>0.0429,0.7559,0.6233,0.0139</t>
-  </si>
-  <si>
-    <t>0.0193,0.5313,0.8723,0.0027</t>
-  </si>
-  <si>
-    <t>0.0918,0.4274,0.7221,0.0147</t>
-  </si>
-  <si>
-    <t>0.0334,0.5046,0.8174,0.0063</t>
-  </si>
-  <si>
-    <t>0.0520,0.4843,0.8076,0.0087</t>
-  </si>
-  <si>
-    <t>0.1257,0.6208,0.4849,0.0384</t>
-  </si>
-  <si>
-    <t>0.2025,0.3124,0.6134,0.0828</t>
-  </si>
-  <si>
-    <t>0.1002,0.3954,0.7344,0.0301</t>
-  </si>
-  <si>
-    <t>0.0990,0.4412,0.6982,0.0459</t>
-  </si>
-  <si>
-    <t>0.1480,0.3972,0.6018,0.0641</t>
-  </si>
-  <si>
-    <t>0.0610,0.6822,0.6064,0.0204</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.7386,0.2111,0.0224,0.0711</t>
+  </si>
+  <si>
+    <t>0.0475,0.0223,0.0047,0.9698</t>
+  </si>
+  <si>
+    <t>0.6321,0.0470,0.0183,0.3619</t>
+  </si>
+  <si>
+    <t>0.0536,0.0436,0.0146,0.9568</t>
+  </si>
+  <si>
+    <t>0.9886,0.0074,0.0015,0.0023</t>
+  </si>
+  <si>
+    <t>0.9815,0.0148,0.0022,0.0035</t>
+  </si>
+  <si>
+    <t>0.9743,0.0220,0.0037,0.0045</t>
+  </si>
+  <si>
+    <t>0.9852,0.0097,0.0021,0.0034</t>
+  </si>
+  <si>
+    <t>0.9760,0.0207,0.0033,0.0038</t>
+  </si>
+  <si>
+    <t>0.9815,0.0209,0.0025,0.0018</t>
+  </si>
+  <si>
+    <t>0.9750,0.0255,0.0024,0.0032</t>
+  </si>
+  <si>
+    <t>0.9834,0.0119,0.0018,0.0034</t>
+  </si>
+  <si>
+    <t>0.2860,0.0739,0.7208,0.0299</t>
+  </si>
+  <si>
+    <t>0.1924,0.4627,0.3560,0.0139</t>
+  </si>
+  <si>
+    <t>0.1387,0.0564,0.8741,0.0035</t>
+  </si>
+  <si>
+    <t>0.1337,0.0988,0.8024,0.0062</t>
+  </si>
+  <si>
+    <t>0.4557,0.2735,0.3158,0.0600</t>
+  </si>
+  <si>
+    <t>0.0024,0.9954,0.0028,0.0017</t>
+  </si>
+  <si>
+    <t>0.0361,0.9563,0.0094,0.0027</t>
+  </si>
+  <si>
+    <t>0.4193,0.6492,0.0225,0.0045</t>
+  </si>
+  <si>
+    <t>0.0112,0.9812,0.0073,0.0031</t>
+  </si>
+  <si>
+    <t>0.0062,0.9899,0.0053,0.0015</t>
+  </si>
+  <si>
+    <t>0.2500,0.0270,0.8202,0.0175</t>
+  </si>
+  <si>
+    <t>0.1954,0.0492,0.8326,0.0165</t>
+  </si>
+  <si>
+    <t>0.0877,0.0094,0.9607,0.0024</t>
+  </si>
+  <si>
+    <t>0.0420,0.0244,0.9693,0.0021</t>
+  </si>
+  <si>
+    <t>0.0476,0.0229,0.9638,0.0013</t>
+  </si>
+  <si>
+    <t>0.0604,0.0167,0.9629,0.0021</t>
+  </si>
+  <si>
+    <t>0.0339,0.0092,0.9522,0.0169</t>
+  </si>
+  <si>
+    <t>0.2359,0.7810,0.0284,0.0093</t>
+  </si>
+  <si>
+    <t>0.2813,0.1414,0.6307,0.0187</t>
+  </si>
+  <si>
+    <t>0.0029,0.0262,0.9923,0.0022</t>
+  </si>
+  <si>
+    <t>0.0152,0.9435,0.1480,0.0021</t>
+  </si>
+  <si>
+    <t>0.7748,0.2065,0.0306,0.0418</t>
+  </si>
+  <si>
+    <t>0.4076,0.1875,0.4264,0.0238</t>
+  </si>
+  <si>
+    <t>0.9276,0.1315,0.0060,0.0023</t>
+  </si>
+  <si>
+    <t>0.0481,0.9031,0.0880,0.0028</t>
+  </si>
+  <si>
+    <t>0.0230,0.8655,0.4765,0.0117</t>
+  </si>
+  <si>
+    <t>0.0458,0.1293,0.9040,0.0156</t>
+  </si>
+  <si>
+    <t>0.0244,0.0727,0.9650,0.0032</t>
+  </si>
+  <si>
+    <t>0.1100,0.0373,0.8855,0.0344</t>
+  </si>
+  <si>
+    <t>0.0307,0.2125,0.9047,0.0052</t>
+  </si>
+  <si>
+    <t>0.0145,0.9543,0.2115,0.0048</t>
+  </si>
+  <si>
+    <t>0.0264,0.0283,0.9764,0.0027</t>
+  </si>
+  <si>
+    <t>0.0820,0.2602,0.0471,0.8692</t>
+  </si>
+  <si>
+    <t>0.0031,0.9879,0.0083,0.0293</t>
+  </si>
+  <si>
+    <t>0.0021,0.9919,0.0389,0.0018</t>
+  </si>
+  <si>
+    <t>0.0035,0.9888,0.0545,0.0019</t>
+  </si>
+  <si>
+    <t>0.0059,0.1247,0.9783,0.0036</t>
+  </si>
+  <si>
+    <t>0.0102,0.2430,0.9611,0.0032</t>
+  </si>
+  <si>
+    <t>0.0954,0.0339,0.9200,0.0076</t>
+  </si>
+  <si>
+    <t>0.0502,0.0069,0.9639,0.0064</t>
+  </si>
+  <si>
+    <t>0.0027,0.0072,0.9945,0.0017</t>
+  </si>
+  <si>
+    <t>0.0467,0.2369,0.8575,0.0052</t>
+  </si>
+  <si>
+    <t>0.9691,0.0306,0.0042,0.0041</t>
+  </si>
+  <si>
+    <t>0.9546,0.0301,0.0092,0.0121</t>
+  </si>
+  <si>
+    <t>0.9159,0.1105,0.0128,0.0098</t>
+  </si>
+  <si>
+    <t>0.0271,0.0551,0.9638,0.0052</t>
+  </si>
+  <si>
+    <t>0.9553,0.0429,0.0085,0.0058</t>
+  </si>
+  <si>
+    <t>0.9785,0.0203,0.0025,0.0031</t>
+  </si>
+  <si>
+    <t>0.9179,0.1361,0.0077,0.0036</t>
+  </si>
+  <si>
+    <t>0.0019,0.9353,0.8658,0.0013</t>
+  </si>
+  <si>
+    <t>0.0051,0.0147,0.9909,0.0022</t>
+  </si>
+  <si>
+    <t>0.0237,0.0277,0.9615,0.0128</t>
+  </si>
+  <si>
+    <t>0.0056,0.8697,0.8529,0.0024</t>
+  </si>
+  <si>
+    <t>0.0155,0.0186,0.9860,0.0018</t>
+  </si>
+  <si>
+    <t>0.0307,0.9609,0.0153,0.0023</t>
+  </si>
+  <si>
+    <t>0.0017,0.9979,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.4746,0.4220,0.2021,0.0361</t>
+  </si>
+  <si>
+    <t>0.4584,0.4059,0.2447,0.0585</t>
+  </si>
+  <si>
+    <t>0.0056,0.0405,0.9875,0.0010</t>
+  </si>
+  <si>
+    <t>0.0019,0.9278,0.8692,0.0017</t>
+  </si>
+  <si>
+    <t>0.0050,0.7705,0.8901,0.0013</t>
+  </si>
+  <si>
+    <t>0.0024,0.9800,0.4748,0.0013</t>
+  </si>
+  <si>
+    <t>0.0068,0.9604,0.4221,0.0052</t>
+  </si>
+  <si>
+    <t>0.0446,0.0085,0.0216,0.9552</t>
+  </si>
+  <si>
+    <t>0.0074,0.0112,0.0037,0.9926</t>
+  </si>
+  <si>
+    <t>0.0238,0.0198,0.0078,0.9796</t>
+  </si>
+  <si>
+    <t>0.0199,0.0181,0.0096,0.9801</t>
+  </si>
+  <si>
+    <t>0.0313,0.0195,0.0087,0.9739</t>
+  </si>
+  <si>
+    <t>0.0085,0.0233,0.0059,0.9902</t>
+  </si>
+  <si>
+    <t>0.0033,0.8747,0.8985,0.0025</t>
+  </si>
+  <si>
+    <t>0.0135,0.3229,0.9438,0.0050</t>
+  </si>
+  <si>
+    <t>0.0191,0.3688,0.9077,0.0041</t>
+  </si>
+  <si>
+    <t>0.0034,0.4940,0.9643,0.0007</t>
+  </si>
+  <si>
+    <t>0.0014,0.9321,0.8763,0.0004</t>
+  </si>
+  <si>
+    <t>0.0151,0.8003,0.6700,0.0054</t>
+  </si>
+  <si>
+    <t>0.9765,0.0275,0.0049,0.0020</t>
+  </si>
+  <si>
+    <t>0.9771,0.0210,0.0040,0.0037</t>
+  </si>
+  <si>
+    <t>0.9359,0.1056,0.0077,0.0033</t>
+  </si>
+  <si>
+    <t>0.9804,0.0178,0.0022,0.0028</t>
+  </si>
+  <si>
+    <t>0.9751,0.0315,0.0040,0.0019</t>
+  </si>
+  <si>
+    <t>0.9787,0.0208,0.0035,0.0029</t>
+  </si>
+  <si>
+    <t>0.9830,0.0171,0.0025,0.0018</t>
+  </si>
+  <si>
+    <t>0.9788,0.0185,0.0023,0.0035</t>
+  </si>
+  <si>
+    <t>0.9873,0.0081,0.0015,0.0032</t>
+  </si>
+  <si>
+    <t>0.9841,0.0157,0.0027,0.0017</t>
+  </si>
+  <si>
+    <t>0.9843,0.0121,0.0037,0.0028</t>
+  </si>
+  <si>
+    <t>0.9879,0.0089,0.0027,0.0020</t>
+  </si>
+  <si>
+    <t>0.9848,0.0142,0.0020,0.0019</t>
+  </si>
+  <si>
+    <t>0.9898,0.0079,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.9862,0.0103,0.0024,0.0024</t>
+  </si>
+  <si>
+    <t>0.9814,0.0125,0.0031,0.0037</t>
+  </si>
+  <si>
+    <t>0.0031,0.0040,0.9922,0.0045</t>
+  </si>
+  <si>
+    <t>0.0916,0.0197,0.9298,0.0087</t>
+  </si>
+  <si>
+    <t>0.6475,0.0355,0.3304,0.0690</t>
+  </si>
+  <si>
+    <t>0.1659,0.0224,0.8984,0.0055</t>
+  </si>
+  <si>
+    <t>0.0455,0.9553,0.0047,0.0016</t>
+  </si>
+  <si>
+    <t>0.0861,0.9328,0.0044,0.0025</t>
+  </si>
+  <si>
+    <t>0.3791,0.7504,0.0079,0.0030</t>
+  </si>
+  <si>
+    <t>0.2969,0.7572,0.0207,0.0062</t>
+  </si>
+  <si>
+    <t>0.1444,0.9017,0.0046,0.0016</t>
+  </si>
+  <si>
+    <t>0.0576,0.9590,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.8305,0.2678,0.0103,0.0058</t>
+  </si>
+  <si>
+    <t>0.3299,0.3979,0.3334,0.0546</t>
+  </si>
+  <si>
+    <t>0.2665,0.0367,0.8000,0.0140</t>
+  </si>
+  <si>
+    <t>0.4009,0.1564,0.4620,0.0268</t>
+  </si>
+  <si>
+    <t>0.3638,0.2198,0.4281,0.0162</t>
+  </si>
+  <si>
+    <t>0.0894,0.6164,0.1278,0.5834</t>
+  </si>
+  <si>
+    <t>0.0063,0.9852,0.0287,0.0021</t>
+  </si>
+  <si>
+    <t>0.0032,0.9917,0.0166,0.0077</t>
+  </si>
+  <si>
+    <t>0.1523,0.7732,0.0995,0.0405</t>
+  </si>
+  <si>
+    <t>0.0009,0.9923,0.2555,0.0016</t>
+  </si>
+  <si>
+    <t>0.0509,0.9405,0.0238,0.0014</t>
+  </si>
+  <si>
+    <t>0.7254,0.3934,0.0145,0.0059</t>
+  </si>
+  <si>
+    <t>0.7433,0.3778,0.0163,0.0040</t>
+  </si>
+  <si>
+    <t>0.9556,0.0385,0.0080,0.0074</t>
+  </si>
+  <si>
+    <t>0.9768,0.0178,0.0046,0.0041</t>
+  </si>
+  <si>
+    <t>0.9787,0.0175,0.0040,0.0031</t>
+  </si>
+  <si>
+    <t>0.9630,0.0305,0.0044,0.0074</t>
+  </si>
+  <si>
+    <t>0.9864,0.0082,0.0022,0.0035</t>
+  </si>
+  <si>
+    <t>0.9655,0.0191,0.0057,0.0103</t>
+  </si>
+  <si>
+    <t>0.9821,0.0169,0.0023,0.0025</t>
+  </si>
+  <si>
+    <t>0.9475,0.0562,0.0053,0.0075</t>
+  </si>
+  <si>
+    <t>0.0235,0.3667,0.9035,0.0087</t>
+  </si>
+  <si>
+    <t>0.0189,0.4183,0.8814,0.0034</t>
+  </si>
+  <si>
+    <t>0.0142,0.1498,0.9629,0.0016</t>
+  </si>
+  <si>
+    <t>0.0166,0.0504,0.9785,0.0012</t>
+  </si>
+  <si>
+    <t>0.4706,0.3080,0.1851,0.0806</t>
+  </si>
+  <si>
+    <t>0.6279,0.1299,0.2784,0.0836</t>
+  </si>
+  <si>
+    <t>0.1285,0.0216,0.8701,0.0285</t>
+  </si>
+  <si>
+    <t>0.3156,0.4552,0.2769,0.1310</t>
+  </si>
+  <si>
+    <t>0.0955,0.0303,0.0301,0.9154</t>
+  </si>
+  <si>
+    <t>0.0012,0.0044,0.0012,0.9983</t>
+  </si>
+  <si>
+    <t>0.0089,0.0208,0.0053,0.9899</t>
+  </si>
+  <si>
+    <t>0.0237,0.0053,0.0061,0.9817</t>
+  </si>
+  <si>
+    <t>0.0039,0.8073,0.8843,0.0032</t>
+  </si>
+  <si>
+    <t>0.9742,0.0189,0.0074,0.0050</t>
+  </si>
+  <si>
+    <t>0.5978,0.4908,0.0208,0.0090</t>
+  </si>
+  <si>
+    <t>0.9488,0.0718,0.0070,0.0044</t>
+  </si>
+  <si>
+    <t>0.8587,0.1958,0.0217,0.0073</t>
+  </si>
+  <si>
+    <t>0.9603,0.0395,0.0075,0.0052</t>
+  </si>
+  <si>
+    <t>0.5385,0.1090,0.2301,0.2417</t>
+  </si>
+  <si>
+    <t>0.9616,0.0306,0.0049,0.0088</t>
+  </si>
+  <si>
+    <t>0.0220,0.0423,0.9625,0.0112</t>
+  </si>
+  <si>
+    <t>0.5487,0.0106,0.0296,0.4780</t>
+  </si>
+  <si>
+    <t>0.5446,0.1423,0.0717,0.3202</t>
+  </si>
+  <si>
+    <t>0.5667,0.4579,0.0617,0.0140</t>
+  </si>
+  <si>
+    <t>0.7844,0.1467,0.1104,0.0097</t>
+  </si>
+  <si>
+    <t>0.9331,0.0541,0.0191,0.0124</t>
+  </si>
+  <si>
+    <t>0.2983,0.6616,0.1193,0.0604</t>
+  </si>
+  <si>
+    <t>0.7116,0.3077,0.0641,0.0118</t>
+  </si>
+  <si>
+    <t>0.5393,0.4852,0.0529,0.0325</t>
+  </si>
+  <si>
+    <t>0.9777,0.0163,0.0033,0.0047</t>
+  </si>
+  <si>
+    <t>0.9724,0.0208,0.0040,0.0057</t>
+  </si>
+  <si>
+    <t>0.9543,0.0472,0.0080,0.0069</t>
+  </si>
+  <si>
+    <t>0.9145,0.0693,0.0178,0.0217</t>
+  </si>
+  <si>
+    <t>0.9784,0.0171,0.0056,0.0031</t>
+  </si>
+  <si>
+    <t>0.9680,0.0276,0.0076,0.0052</t>
+  </si>
+  <si>
+    <t>0.9672,0.0248,0.0071,0.0066</t>
+  </si>
+  <si>
+    <t>0.9649,0.0286,0.0051,0.0071</t>
+  </si>
+  <si>
+    <t>0.6656,0.4109,0.0360,0.0090</t>
+  </si>
+  <si>
+    <t>0.7348,0.3492,0.0347,0.0116</t>
+  </si>
+  <si>
+    <t>0.4342,0.7152,0.0096,0.0038</t>
+  </si>
+  <si>
+    <t>0.3883,0.5887,0.1440,0.0199</t>
+  </si>
+  <si>
+    <t>0.9639,0.0368,0.0067,0.0041</t>
+  </si>
+  <si>
+    <t>0.9325,0.1011,0.0076,0.0042</t>
+  </si>
+  <si>
+    <t>0.9541,0.0417,0.0065,0.0082</t>
+  </si>
+  <si>
+    <t>0.9406,0.0881,0.0091,0.0027</t>
+  </si>
+  <si>
+    <t>0.0106,0.0645,0.9830,0.0016</t>
+  </si>
+  <si>
+    <t>0.9443,0.0591,0.0179,0.0069</t>
+  </si>
+  <si>
+    <t>0.0074,0.0172,0.9912,0.0013</t>
+  </si>
+  <si>
+    <t>0.0079,0.0544,0.9821,0.0019</t>
+  </si>
+  <si>
+    <t>0.1084,0.0582,0.8886,0.0066</t>
+  </si>
+  <si>
+    <t>0.0025,0.0305,0.9951,0.0004</t>
+  </si>
+  <si>
+    <t>0.0269,0.0117,0.9756,0.0039</t>
+  </si>
+  <si>
+    <t>0.0165,0.0038,0.9915,0.0006</t>
+  </si>
+  <si>
+    <t>0.0147,0.0119,0.9894,0.0010</t>
+  </si>
+  <si>
+    <t>0.1729,0.1651,0.7311,0.0208</t>
+  </si>
+  <si>
+    <t>0.1685,0.0607,0.8348,0.0152</t>
+  </si>
+  <si>
+    <t>0.2873,0.1412,0.5832,0.0322</t>
+  </si>
+  <si>
+    <t>0.1702,0.1600,0.7050,0.0105</t>
+  </si>
+  <si>
+    <t>0.0999,0.4040,0.5708,0.0087</t>
+  </si>
+  <si>
+    <t>0.1594,0.1830,0.6994,0.0166</t>
+  </si>
+  <si>
+    <t>0.2828,0.0345,0.7145,0.0353</t>
+  </si>
+  <si>
+    <t>0.0980,0.2467,0.7227,0.0052</t>
+  </si>
+  <si>
+    <t>0.6171,0.5141,0.0241,0.0044</t>
+  </si>
+  <si>
+    <t>0.7613,0.3684,0.0156,0.0041</t>
+  </si>
+  <si>
+    <t>0.7938,0.3292,0.0121,0.0036</t>
+  </si>
+  <si>
+    <t>0.9473,0.0615,0.0108,0.0052</t>
+  </si>
+  <si>
+    <t>0.9315,0.1024,0.0097,0.0035</t>
+  </si>
+  <si>
+    <t>0.3345,0.1569,0.5181,0.0535</t>
+  </si>
+  <si>
+    <t>0.5336,0.2047,0.3010,0.0466</t>
+  </si>
+  <si>
+    <t>0.5359,0.0487,0.5011,0.0503</t>
+  </si>
+  <si>
+    <t>0.5356,0.0808,0.4169,0.0804</t>
+  </si>
+  <si>
+    <t>0.8090,0.0945,0.1053,0.0323</t>
+  </si>
+  <si>
+    <t>0.0373,0.0168,0.9528,0.0122</t>
+  </si>
+  <si>
+    <t>0.0386,0.0381,0.9471,0.0123</t>
+  </si>
+  <si>
+    <t>0.0585,0.0791,0.9167,0.0164</t>
+  </si>
+  <si>
+    <t>0.0550,0.0467,0.9359,0.0120</t>
+  </si>
+  <si>
+    <t>0.0116,0.3917,0.9224,0.0020</t>
+  </si>
+  <si>
+    <t>0.9799,0.0148,0.0028,0.0043</t>
+  </si>
+  <si>
+    <t>0.9756,0.0244,0.0028,0.0030</t>
+  </si>
+  <si>
+    <t>0.9740,0.0192,0.0037,0.0054</t>
+  </si>
+  <si>
+    <t>0.9541,0.0627,0.0068,0.0034</t>
+  </si>
+  <si>
+    <t>0.9749,0.0244,0.0044,0.0033</t>
+  </si>
+  <si>
+    <t>0.9818,0.0181,0.0023,0.0022</t>
+  </si>
+  <si>
+    <t>0.9752,0.0266,0.0043,0.0025</t>
+  </si>
+  <si>
+    <t>0.9598,0.0345,0.0067,0.0076</t>
+  </si>
+  <si>
+    <t>0.1088,0.3331,0.7188,0.0165</t>
+  </si>
+  <si>
+    <t>0.2125,0.6476,0.2169,0.0187</t>
+  </si>
+  <si>
+    <t>0.8464,0.0899,0.0970,0.0165</t>
+  </si>
+  <si>
+    <t>0.0322,0.0183,0.9740,0.0028</t>
+  </si>
+  <si>
+    <t>0.0078,0.0397,0.9682,0.0201</t>
+  </si>
+  <si>
+    <t>0.0222,0.0278,0.9714,0.0041</t>
+  </si>
+  <si>
+    <t>0.0053,0.0068,0.9914,0.0029</t>
+  </si>
+  <si>
+    <t>0.0464,0.0544,0.9464,0.0038</t>
+  </si>
+  <si>
+    <t>0.0037,0.0262,0.9924,0.0016</t>
+  </si>
+  <si>
+    <t>0.0660,0.0391,0.9230,0.0191</t>
+  </si>
+  <si>
+    <t>0.1260,0.0712,0.8493,0.0091</t>
+  </si>
+  <si>
+    <t>0.5861,0.0504,0.4516,0.0394</t>
+  </si>
+  <si>
+    <t>0.4690,0.0213,0.6729,0.0169</t>
+  </si>
+  <si>
+    <t>0.6909,0.0428,0.3154,0.0503</t>
+  </si>
+  <si>
+    <t>0.9739,0.0257,0.0034,0.0033</t>
+  </si>
+  <si>
+    <t>0.9705,0.0344,0.0057,0.0025</t>
+  </si>
+  <si>
+    <t>0.9751,0.0249,0.0064,0.0027</t>
+  </si>
+  <si>
+    <t>0.9791,0.0183,0.0023,0.0038</t>
+  </si>
+  <si>
+    <t>0.9710,0.0289,0.0041,0.0038</t>
+  </si>
+  <si>
+    <t>0.9720,0.0294,0.0077,0.0030</t>
+  </si>
+  <si>
+    <t>0.9687,0.0389,0.0029,0.0032</t>
+  </si>
+  <si>
+    <t>0.9724,0.0317,0.0033,0.0030</t>
+  </si>
+  <si>
+    <t>0.0263,0.2984,0.8857,0.0101</t>
+  </si>
+  <si>
+    <t>0.0091,0.0580,0.9753,0.0044</t>
+  </si>
+  <si>
+    <t>0.0081,0.0400,0.9865,0.0016</t>
+  </si>
+  <si>
+    <t>0.1137,0.0910,0.8458,0.0070</t>
+  </si>
+  <si>
+    <t>0.0108,0.0053,0.9807,0.0082</t>
+  </si>
+  <si>
+    <t>0.1363,0.0205,0.9242,0.0060</t>
+  </si>
+  <si>
+    <t>0.0478,0.0650,0.9160,0.0184</t>
+  </si>
+  <si>
+    <t>0.0784,0.0553,0.8806,0.0479</t>
+  </si>
+  <si>
+    <t>0.7045,0.0316,0.0200,0.3101</t>
+  </si>
+  <si>
+    <t>0.0039,0.0901,0.0036,0.9935</t>
+  </si>
+  <si>
+    <t>0.0963,0.0063,0.0049,0.9452</t>
+  </si>
+  <si>
+    <t>0.0074,0.0015,0.0011,0.9955</t>
+  </si>
+  <si>
+    <t>0.0174,0.0107,0.0067,0.9848</t>
+  </si>
+  <si>
+    <t>0.4488,0.1144,0.0494,0.4725</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1956,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1984,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,10 +2012,10 @@
         <v>259</v>
       </c>
       <c r="C6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,10 +2026,10 @@
         <v>259</v>
       </c>
       <c r="C7" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,10 +2040,10 @@
         <v>259</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,10 +2054,10 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,10 +2068,10 @@
         <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,10 +2082,10 @@
         <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,10 +2096,10 @@
         <v>259</v>
       </c>
       <c r="C12" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,10 +2110,10 @@
         <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2124,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2180,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,10 +2236,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,10 +2250,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2281,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2323,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2337,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,10 +2390,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,10 +2418,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2432,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2446,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2505,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2586,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,10 +2600,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,10 +2614,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2628,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2642,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,10 +2684,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,10 +2712,10 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,10 +2726,10 @@
         <v>259</v>
       </c>
       <c r="C57" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,10 +2740,10 @@
         <v>259</v>
       </c>
       <c r="C58" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,10 +2768,10 @@
         <v>259</v>
       </c>
       <c r="C60" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,10 +2782,10 @@
         <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,10 +2796,10 @@
         <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2824,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2908,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2953,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2967,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2978,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3149,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3163,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,10 +3174,10 @@
         <v>259</v>
       </c>
       <c r="C89" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,10 +3188,10 @@
         <v>259</v>
       </c>
       <c r="C90" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,10 +3202,10 @@
         <v>259</v>
       </c>
       <c r="C91" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,10 +3216,10 @@
         <v>259</v>
       </c>
       <c r="C92" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,10 +3230,10 @@
         <v>259</v>
       </c>
       <c r="C93" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,10 +3244,10 @@
         <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,10 +3258,10 @@
         <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,10 +3272,10 @@
         <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,10 +3286,10 @@
         <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,10 +3300,10 @@
         <v>259</v>
       </c>
       <c r="C98" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,10 +3314,10 @@
         <v>259</v>
       </c>
       <c r="C99" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,10 +3328,10 @@
         <v>259</v>
       </c>
       <c r="C100" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,10 +3342,10 @@
         <v>259</v>
       </c>
       <c r="C101" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,10 +3356,10 @@
         <v>259</v>
       </c>
       <c r="C102" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,10 +3370,10 @@
         <v>259</v>
       </c>
       <c r="C103" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,10 +3384,10 @@
         <v>259</v>
       </c>
       <c r="C104" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3426,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,10 +3454,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3482,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3496,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3538,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3552,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3580,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,10 +3622,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,10 +3636,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3667,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3692,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3706,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,10 +3720,10 @@
         <v>259</v>
       </c>
       <c r="C128" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,10 +3734,10 @@
         <v>259</v>
       </c>
       <c r="C129" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,10 +3748,10 @@
         <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,10 +3762,10 @@
         <v>259</v>
       </c>
       <c r="C131" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,10 +3776,10 @@
         <v>259</v>
       </c>
       <c r="C132" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,10 +3790,10 @@
         <v>259</v>
       </c>
       <c r="C133" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,10 +3804,10 @@
         <v>259</v>
       </c>
       <c r="C134" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,10 +3818,10 @@
         <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3888,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3902,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3919,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3930,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4003,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,10 +4014,10 @@
         <v>259</v>
       </c>
       <c r="C149" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,10 +4042,10 @@
         <v>259</v>
       </c>
       <c r="C151" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4056,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,10 +4070,10 @@
         <v>259</v>
       </c>
       <c r="C153" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4084,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,10 +4098,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4112,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4126,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,10 +4140,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4154,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,10 +4168,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,10 +4182,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4210,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,10 +4224,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,10 +4238,10 @@
         <v>259</v>
       </c>
       <c r="C165" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,10 +4252,10 @@
         <v>259</v>
       </c>
       <c r="C166" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,10 +4266,10 @@
         <v>259</v>
       </c>
       <c r="C167" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,10 +4280,10 @@
         <v>259</v>
       </c>
       <c r="C168" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,10 +4294,10 @@
         <v>259</v>
       </c>
       <c r="C169" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,10 +4308,10 @@
         <v>259</v>
       </c>
       <c r="C170" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,10 +4322,10 @@
         <v>259</v>
       </c>
       <c r="C171" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,10 +4336,10 @@
         <v>259</v>
       </c>
       <c r="C172" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4350,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4378,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,10 +4406,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,10 +4420,10 @@
         <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,10 +4434,10 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,10 +4448,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4462,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,10 +4476,10 @@
         <v>259</v>
       </c>
       <c r="C182" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,10 +4490,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4532,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,10 +4574,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4591,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4605,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4672,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4689,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4728,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,10 +4742,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4756,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4770,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4784,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4798,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4812,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4826,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4871,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4899,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,10 +4910,10 @@
         <v>259</v>
       </c>
       <c r="C213" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,10 +4924,10 @@
         <v>259</v>
       </c>
       <c r="C214" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,10 +4938,10 @@
         <v>259</v>
       </c>
       <c r="C215" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,10 +4952,10 @@
         <v>259</v>
       </c>
       <c r="C216" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,10 +4966,10 @@
         <v>259</v>
       </c>
       <c r="C217" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,10 +4980,10 @@
         <v>259</v>
       </c>
       <c r="C218" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,10 +4994,10 @@
         <v>259</v>
       </c>
       <c r="C219" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,10 +5008,10 @@
         <v>259</v>
       </c>
       <c r="C220" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,10 +5050,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,10 +5106,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5123,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5176,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5204,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,10 +5218,10 @@
         <v>259</v>
       </c>
       <c r="C235" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,10 +5232,10 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,10 +5246,10 @@
         <v>259</v>
       </c>
       <c r="C237" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5257,10 +5260,10 @@
         <v>259</v>
       </c>
       <c r="C238" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,10 +5274,10 @@
         <v>259</v>
       </c>
       <c r="C239" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5285,10 +5288,10 @@
         <v>259</v>
       </c>
       <c r="C240" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,10 +5302,10 @@
         <v>259</v>
       </c>
       <c r="C241" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5313,10 +5316,10 @@
         <v>259</v>
       </c>
       <c r="C242" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5344,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5358,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5403,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5431,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5442,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5512,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
